--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202605/Currency_P&L_20260501.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202605/Currency_P&L_20260501.xlsx
@@ -27581,31 +27581,31 @@
         <v>46143</v>
       </c>
       <c r="B1111">
-        <v>91094854.09</v>
+        <v>92552592.2</v>
       </c>
       <c r="C1111">
-        <v>-43371.79</v>
+        <v>-29509.65</v>
       </c>
       <c r="D1111">
-        <v>-0.000476</v>
+        <v>-0.000324</v>
       </c>
       <c r="E1111">
-        <v>-543938.63</v>
+        <v>185880.6</v>
       </c>
       <c r="F1111">
-        <v>-0.005971</v>
+        <v>0.002041</v>
       </c>
       <c r="O1111">
-        <v>-35155.59</v>
+        <v>3895.86</v>
       </c>
       <c r="P1111">
-        <v>-0.000386</v>
+        <v>4.3E-05</v>
       </c>
       <c r="Q1111">
-        <v>-31035.56</v>
+        <v>0</v>
       </c>
       <c r="R1111">
-        <v>-0.000341</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
